--- a/summary.xlsx
+++ b/summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vub-my.sharepoint.com/personal/menthy_denayer_vub_be/Documents/PhD-Main/[01] main/WP1/T1.2/[01] results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medenaye\Documents\programs\GitHub\Predictive-MSK-Comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="470" documentId="13_ncr:1_{64A46DF4-D22D-444E-BAEB-57E621CC6FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBAE3A75-6386-4EC7-ADA5-6A20BD93C455}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07AFFE26-2AE4-4504-8B9B-95385106C5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="45">
   <si>
     <t>method</t>
   </si>
@@ -165,6 +165,12 @@
   </si>
   <si>
     <t>total avg</t>
+  </si>
+  <si>
+    <t>RMSE (N/kg)</t>
+  </si>
+  <si>
+    <t>RMSE (Nm/kg)</t>
   </si>
 </sst>
 </file>
@@ -395,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -489,6 +495,39 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -498,45 +537,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -544,18 +544,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -860,90 +848,90 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="50"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="45"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="51" t="s">
+      <c r="N2" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="52"/>
-      <c r="P2" s="52"/>
-      <c r="Q2" s="52"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="52"/>
-      <c r="T2" s="52"/>
-      <c r="U2" s="52"/>
-      <c r="V2" s="52"/>
-      <c r="W2" s="52"/>
-      <c r="X2" s="53"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
+      <c r="V2" s="50"/>
+      <c r="W2" s="50"/>
+      <c r="X2" s="51"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" s="51" t="s">
+      <c r="Z2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="AA2" s="52"/>
-      <c r="AB2" s="52"/>
-      <c r="AC2" s="52"/>
-      <c r="AD2" s="52"/>
-      <c r="AE2" s="52"/>
-      <c r="AF2" s="52"/>
-      <c r="AG2" s="52"/>
-      <c r="AH2" s="52"/>
-      <c r="AI2" s="52"/>
-      <c r="AJ2" s="53"/>
+      <c r="AA2" s="50"/>
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="50"/>
+      <c r="AE2" s="50"/>
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="51"/>
     </row>
     <row r="3" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="37"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="48"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="35" t="s">
+      <c r="N3" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="36"/>
-      <c r="P3" s="36"/>
-      <c r="Q3" s="36"/>
-      <c r="R3" s="36"/>
-      <c r="S3" s="36"/>
-      <c r="T3" s="36"/>
-      <c r="U3" s="36"/>
-      <c r="V3" s="36"/>
-      <c r="W3" s="36"/>
-      <c r="X3" s="37"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="47"/>
+      <c r="V3" s="47"/>
+      <c r="W3" s="47"/>
+      <c r="X3" s="48"/>
       <c r="Y3" s="1"/>
-      <c r="Z3" s="35" t="s">
+      <c r="Z3" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="AA3" s="36"/>
-      <c r="AB3" s="36"/>
-      <c r="AC3" s="36"/>
-      <c r="AD3" s="36"/>
-      <c r="AE3" s="36"/>
-      <c r="AF3" s="36"/>
-      <c r="AG3" s="36"/>
-      <c r="AH3" s="36"/>
-      <c r="AI3" s="36"/>
-      <c r="AJ3" s="37"/>
+      <c r="AA3" s="47"/>
+      <c r="AB3" s="47"/>
+      <c r="AC3" s="47"/>
+      <c r="AD3" s="47"/>
+      <c r="AE3" s="47"/>
+      <c r="AF3" s="47"/>
+      <c r="AG3" s="47"/>
+      <c r="AH3" s="47"/>
+      <c r="AI3" s="47"/>
+      <c r="AJ3" s="48"/>
     </row>
     <row r="4" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B4" s="31" t="s">
@@ -1082,7 +1070,7 @@
         <f>AVERAGE(I5:J5)</f>
         <v>3.87</v>
       </c>
-      <c r="L5" s="38">
+      <c r="L5" s="35">
         <f>AVERAGE(E5,H5,K5)</f>
         <v>4.6466666666666674</v>
       </c>
@@ -1120,7 +1108,7 @@
         <f>AVERAGE(U5:V5)</f>
         <v>0.86</v>
       </c>
-      <c r="X5" s="38">
+      <c r="X5" s="35">
         <f>AVERAGE(Q5,T5,W5)</f>
         <v>0.94</v>
       </c>
@@ -1158,7 +1146,7 @@
         <f>AVERAGE(AG5:AH5)</f>
         <v>76.734999999999999</v>
       </c>
-      <c r="AJ5" s="38">
+      <c r="AJ5" s="35">
         <f>AVERAGE(AC5,AF5,AI5)</f>
         <v>83.83</v>
       </c>
@@ -1235,7 +1223,7 @@
         <f t="shared" ref="W6:W9" si="6">AVERAGE(U6:V6)</f>
         <v>0.82499999999999996</v>
       </c>
-      <c r="X6" s="38">
+      <c r="X6" s="35">
         <f t="shared" ref="X6:X9" si="7">AVERAGE(Q6,T6,W6)</f>
         <v>0.89499999999999991</v>
       </c>
@@ -1312,7 +1300,7 @@
         <f t="shared" si="2"/>
         <v>8.745000000000001</v>
       </c>
-      <c r="L7" s="38">
+      <c r="L7" s="35">
         <f t="shared" si="3"/>
         <v>6.0433333333333339</v>
       </c>
@@ -1388,7 +1376,7 @@
         <f t="shared" si="10"/>
         <v>40.094999999999999</v>
       </c>
-      <c r="AJ7" s="38">
+      <c r="AJ7" s="35">
         <f t="shared" si="11"/>
         <v>71.451666666666668</v>
       </c>
@@ -1698,47 +1686,47 @@
       <c r="AJ11" s="1"/>
     </row>
     <row r="12" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B12" s="48" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="49"/>
-      <c r="L12" s="50"/>
+      <c r="B12" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="45"/>
       <c r="M12" s="1"/>
-      <c r="N12" s="48" t="s">
+      <c r="N12" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="49"/>
-      <c r="P12" s="49"/>
-      <c r="Q12" s="49"/>
-      <c r="R12" s="49"/>
-      <c r="S12" s="49"/>
-      <c r="T12" s="49"/>
-      <c r="U12" s="49"/>
-      <c r="V12" s="49"/>
-      <c r="W12" s="49"/>
-      <c r="X12" s="50"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
+      <c r="T12" s="44"/>
+      <c r="U12" s="44"/>
+      <c r="V12" s="44"/>
+      <c r="W12" s="44"/>
+      <c r="X12" s="45"/>
       <c r="Y12" s="1"/>
-      <c r="Z12" s="48" t="s">
+      <c r="Z12" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="AA12" s="49"/>
-      <c r="AB12" s="49"/>
-      <c r="AC12" s="49"/>
-      <c r="AD12" s="49"/>
-      <c r="AE12" s="49"/>
-      <c r="AF12" s="49"/>
-      <c r="AG12" s="49"/>
-      <c r="AH12" s="49"/>
-      <c r="AI12" s="49"/>
-      <c r="AJ12" s="50"/>
+      <c r="AA12" s="44"/>
+      <c r="AB12" s="44"/>
+      <c r="AC12" s="44"/>
+      <c r="AD12" s="44"/>
+      <c r="AE12" s="44"/>
+      <c r="AF12" s="44"/>
+      <c r="AG12" s="44"/>
+      <c r="AH12" s="44"/>
+      <c r="AI12" s="44"/>
+      <c r="AJ12" s="45"/>
     </row>
     <row r="13" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -1829,30 +1817,30 @@
       <c r="B14" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="42">
+      <c r="C14" s="1">
         <v>0.22</v>
       </c>
-      <c r="D14" s="42">
+      <c r="D14" s="1">
         <v>0.23</v>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="20">
         <f>AVERAGE(C14:D14)</f>
         <v>0.22500000000000001</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="1">
         <v>0.78</v>
       </c>
-      <c r="G14" s="42">
+      <c r="G14" s="1">
         <v>0.83</v>
       </c>
-      <c r="H14" s="43">
+      <c r="H14" s="20">
         <f>AVERAGE(F14:G14)</f>
         <v>0.80499999999999994</v>
       </c>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
       <c r="K14" s="6"/>
-      <c r="L14" s="45">
+      <c r="L14" s="38">
         <f>AVERAGE(E14,H14)</f>
         <v>0.51500000000000001</v>
       </c>
@@ -1860,30 +1848,30 @@
       <c r="N14" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="O14" s="42">
+      <c r="O14" s="1">
         <v>0.96</v>
       </c>
-      <c r="P14" s="42">
+      <c r="P14" s="1">
         <v>0.95</v>
       </c>
-      <c r="Q14" s="43">
+      <c r="Q14" s="20">
         <f>AVERAGE(O14:P14)</f>
         <v>0.95499999999999996</v>
       </c>
-      <c r="R14" s="42">
+      <c r="R14" s="1">
         <v>0.98</v>
       </c>
-      <c r="S14" s="42">
+      <c r="S14" s="1">
         <v>0.98</v>
       </c>
-      <c r="T14" s="43">
+      <c r="T14" s="20">
         <f>AVERAGE(R14:S14)</f>
         <v>0.98</v>
       </c>
-      <c r="U14" s="42"/>
-      <c r="V14" s="42"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
       <c r="W14" s="6"/>
-      <c r="X14" s="45">
+      <c r="X14" s="38">
         <f>AVERAGE(Q14,T14)</f>
         <v>0.96750000000000003</v>
       </c>
@@ -1891,30 +1879,30 @@
       <c r="Z14" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="AA14" s="42">
+      <c r="AA14" s="1">
         <v>78.22</v>
       </c>
-      <c r="AB14" s="42">
+      <c r="AB14" s="1">
         <v>74.260000000000005</v>
       </c>
-      <c r="AC14" s="43">
+      <c r="AC14" s="20">
         <f>AVERAGE(AA14:AB14)</f>
         <v>76.240000000000009</v>
       </c>
-      <c r="AD14" s="42">
+      <c r="AD14" s="1">
         <v>75.25</v>
       </c>
-      <c r="AE14" s="42">
+      <c r="AE14" s="1">
         <v>73.27</v>
       </c>
-      <c r="AF14" s="43">
+      <c r="AF14" s="20">
         <f>AVERAGE(AD14:AE14)</f>
         <v>74.259999999999991</v>
       </c>
-      <c r="AG14" s="42"/>
-      <c r="AH14" s="42"/>
+      <c r="AG14" s="1"/>
+      <c r="AH14" s="1"/>
       <c r="AI14" s="6"/>
-      <c r="AJ14" s="45">
+      <c r="AJ14" s="38">
         <f>AVERAGE(AC14,AF14)</f>
         <v>75.25</v>
       </c>
@@ -1923,30 +1911,30 @@
       <c r="B15" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="42">
+      <c r="C15" s="1">
         <v>0.33</v>
       </c>
-      <c r="D15" s="42">
+      <c r="D15" s="1">
         <v>0.34</v>
       </c>
-      <c r="E15" s="44">
+      <c r="E15" s="13">
         <f t="shared" ref="E15:E18" si="12">AVERAGE(C15:D15)</f>
         <v>0.33500000000000002</v>
       </c>
-      <c r="F15" s="42">
+      <c r="F15" s="1">
         <v>1.29</v>
       </c>
-      <c r="G15" s="42">
+      <c r="G15" s="1">
         <v>1.32</v>
       </c>
-      <c r="H15" s="44">
+      <c r="H15" s="13">
         <f t="shared" ref="H15:H18" si="13">AVERAGE(F15:G15)</f>
         <v>1.3050000000000002</v>
       </c>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
       <c r="K15" s="6"/>
-      <c r="L15" s="45">
+      <c r="L15" s="38">
         <f>AVERAGE(E15,H15)</f>
         <v>0.82000000000000006</v>
       </c>
@@ -1954,30 +1942,30 @@
       <c r="N15" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="O15" s="42">
+      <c r="O15" s="1">
         <v>0.92</v>
       </c>
-      <c r="P15" s="42">
+      <c r="P15" s="1">
         <v>0.93</v>
       </c>
-      <c r="Q15" s="44">
+      <c r="Q15" s="13">
         <f t="shared" ref="Q15:Q18" si="14">AVERAGE(O15:P15)</f>
         <v>0.92500000000000004</v>
       </c>
-      <c r="R15" s="42">
+      <c r="R15" s="1">
         <v>0.96</v>
       </c>
-      <c r="S15" s="42">
+      <c r="S15" s="1">
         <v>0.96</v>
       </c>
-      <c r="T15" s="44">
+      <c r="T15" s="13">
         <f t="shared" ref="T15:T18" si="15">AVERAGE(R15:S15)</f>
         <v>0.96</v>
       </c>
-      <c r="U15" s="42"/>
-      <c r="V15" s="42"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
       <c r="W15" s="6"/>
-      <c r="X15" s="45">
+      <c r="X15" s="38">
         <f>AVERAGE(Q15,T15)</f>
         <v>0.9425</v>
       </c>
@@ -1985,30 +1973,30 @@
       <c r="Z15" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="AA15" s="42">
+      <c r="AA15" s="1">
         <v>76.239999999999995</v>
       </c>
-      <c r="AB15" s="42">
+      <c r="AB15" s="1">
         <v>71.290000000000006</v>
       </c>
-      <c r="AC15" s="44">
+      <c r="AC15" s="13">
         <f t="shared" ref="AC15:AC18" si="16">AVERAGE(AA15:AB15)</f>
         <v>73.765000000000001</v>
       </c>
-      <c r="AD15" s="42">
+      <c r="AD15" s="1">
         <v>64.36</v>
       </c>
-      <c r="AE15" s="42">
+      <c r="AE15" s="1">
         <v>66.34</v>
       </c>
-      <c r="AF15" s="44">
+      <c r="AF15" s="13">
         <f t="shared" ref="AF15:AF18" si="17">AVERAGE(AD15:AE15)</f>
         <v>65.349999999999994</v>
       </c>
-      <c r="AG15" s="42"/>
-      <c r="AH15" s="42"/>
+      <c r="AG15" s="1"/>
+      <c r="AH15" s="1"/>
       <c r="AI15" s="6"/>
-      <c r="AJ15" s="45">
+      <c r="AJ15" s="38">
         <f>AVERAGE(AC15,AF15)</f>
         <v>69.557500000000005</v>
       </c>
@@ -2017,30 +2005,30 @@
       <c r="B16" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="1">
         <v>0.44</v>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="1">
         <v>0.44</v>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="13">
         <f t="shared" si="12"/>
         <v>0.44</v>
       </c>
-      <c r="F16" s="42">
+      <c r="F16" s="1">
         <v>1.76</v>
       </c>
-      <c r="G16" s="42">
+      <c r="G16" s="1">
         <v>1.78</v>
       </c>
-      <c r="H16" s="44">
+      <c r="H16" s="13">
         <f t="shared" si="13"/>
         <v>1.77</v>
       </c>
-      <c r="I16" s="42"/>
-      <c r="J16" s="42"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
       <c r="K16" s="6"/>
-      <c r="L16" s="46">
+      <c r="L16" s="39">
         <f>AVERAGE(E16,H16)</f>
         <v>1.105</v>
       </c>
@@ -2048,30 +2036,30 @@
       <c r="N16" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="O16" s="42">
+      <c r="O16" s="1">
         <v>0.85</v>
       </c>
-      <c r="P16" s="42">
+      <c r="P16" s="1">
         <v>0.86</v>
       </c>
-      <c r="Q16" s="44">
+      <c r="Q16" s="13">
         <f t="shared" si="14"/>
         <v>0.85499999999999998</v>
       </c>
-      <c r="R16" s="42">
+      <c r="R16" s="1">
         <v>0.93</v>
       </c>
-      <c r="S16" s="42">
+      <c r="S16" s="1">
         <v>0.93</v>
       </c>
-      <c r="T16" s="44">
+      <c r="T16" s="13">
         <f t="shared" si="15"/>
         <v>0.93</v>
       </c>
-      <c r="U16" s="42"/>
-      <c r="V16" s="42"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1"/>
       <c r="W16" s="6"/>
-      <c r="X16" s="46">
+      <c r="X16" s="39">
         <f>AVERAGE(Q16,T16)</f>
         <v>0.89250000000000007</v>
       </c>
@@ -2079,30 +2067,30 @@
       <c r="Z16" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="AA16" s="42">
+      <c r="AA16" s="1">
         <v>46.53</v>
       </c>
-      <c r="AB16" s="42">
+      <c r="AB16" s="1">
         <v>51.49</v>
       </c>
-      <c r="AC16" s="44">
+      <c r="AC16" s="13">
         <f t="shared" si="16"/>
         <v>49.010000000000005</v>
       </c>
-      <c r="AD16" s="42">
+      <c r="AD16" s="1">
         <v>71.290000000000006</v>
       </c>
-      <c r="AE16" s="42">
+      <c r="AE16" s="1">
         <v>67.33</v>
       </c>
-      <c r="AF16" s="44">
+      <c r="AF16" s="13">
         <f t="shared" si="17"/>
         <v>69.31</v>
       </c>
-      <c r="AG16" s="42"/>
-      <c r="AH16" s="42"/>
+      <c r="AG16" s="1"/>
+      <c r="AH16" s="1"/>
       <c r="AI16" s="6"/>
-      <c r="AJ16" s="46">
+      <c r="AJ16" s="39">
         <f>AVERAGE(AC16,AF16)</f>
         <v>59.160000000000004</v>
       </c>
@@ -2111,30 +2099,30 @@
       <c r="B17" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="42">
+      <c r="C17" s="1">
         <v>0.44</v>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="1">
         <v>0.36</v>
       </c>
-      <c r="E17" s="44">
+      <c r="E17" s="13">
         <f t="shared" si="12"/>
         <v>0.4</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="1">
         <v>1.1399999999999999</v>
       </c>
-      <c r="G17" s="42">
+      <c r="G17" s="1">
         <v>1.76</v>
       </c>
-      <c r="H17" s="44">
+      <c r="H17" s="13">
         <f t="shared" si="13"/>
         <v>1.45</v>
       </c>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
       <c r="K17" s="6"/>
-      <c r="L17" s="46">
+      <c r="L17" s="39">
         <f>AVERAGE(E17,H17)</f>
         <v>0.92500000000000004</v>
       </c>
@@ -2142,30 +2130,30 @@
       <c r="N17" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="O17" s="42">
+      <c r="O17" s="1">
         <v>0.88</v>
       </c>
-      <c r="P17" s="42">
+      <c r="P17" s="1">
         <v>0.9</v>
       </c>
-      <c r="Q17" s="44">
+      <c r="Q17" s="13">
         <f t="shared" si="14"/>
         <v>0.89</v>
       </c>
-      <c r="R17" s="42">
+      <c r="R17" s="1">
         <v>0.96</v>
       </c>
-      <c r="S17" s="42">
+      <c r="S17" s="1">
         <v>0.91</v>
       </c>
-      <c r="T17" s="44">
+      <c r="T17" s="13">
         <f t="shared" si="15"/>
         <v>0.93500000000000005</v>
       </c>
-      <c r="U17" s="42"/>
-      <c r="V17" s="42"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
       <c r="W17" s="6"/>
-      <c r="X17" s="46">
+      <c r="X17" s="39">
         <f>AVERAGE(Q17,T17)</f>
         <v>0.91250000000000009</v>
       </c>
@@ -2173,30 +2161,30 @@
       <c r="Z17" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AA17" s="42">
+      <c r="AA17" s="1">
         <v>63.37</v>
       </c>
-      <c r="AB17" s="42">
+      <c r="AB17" s="1">
         <v>59.41</v>
       </c>
-      <c r="AC17" s="44">
+      <c r="AC17" s="13">
         <f t="shared" si="16"/>
         <v>61.39</v>
       </c>
-      <c r="AD17" s="42">
+      <c r="AD17" s="1">
         <v>57.43</v>
       </c>
-      <c r="AE17" s="42">
+      <c r="AE17" s="1">
         <v>39.6</v>
       </c>
-      <c r="AF17" s="44">
+      <c r="AF17" s="13">
         <f t="shared" si="17"/>
         <v>48.515000000000001</v>
       </c>
-      <c r="AG17" s="42"/>
-      <c r="AH17" s="42"/>
+      <c r="AG17" s="1"/>
+      <c r="AH17" s="1"/>
       <c r="AI17" s="6"/>
-      <c r="AJ17" s="46">
+      <c r="AJ17" s="39">
         <f>AVERAGE(AC17,AF17)</f>
         <v>54.952500000000001</v>
       </c>
@@ -2228,7 +2216,7 @@
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
       <c r="K18" s="9"/>
-      <c r="L18" s="47">
+      <c r="L18" s="40">
         <f>AVERAGE(E18,H18)</f>
         <v>1.2374999999999998</v>
       </c>
@@ -2259,7 +2247,7 @@
       <c r="U18" s="8"/>
       <c r="V18" s="8"/>
       <c r="W18" s="9"/>
-      <c r="X18" s="47">
+      <c r="X18" s="40">
         <f>AVERAGE(Q18,T18)</f>
         <v>0.82499999999999996</v>
       </c>
@@ -2290,7 +2278,7 @@
       <c r="AG18" s="8"/>
       <c r="AH18" s="8"/>
       <c r="AI18" s="9"/>
-      <c r="AJ18" s="47">
+      <c r="AJ18" s="40">
         <f>AVERAGE(AC18,AF18)</f>
         <v>54.457499999999996</v>
       </c>
@@ -2370,90 +2358,90 @@
       <c r="AJ20" s="1"/>
     </row>
     <row r="21" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B21" s="51" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="52"/>
-      <c r="K21" s="52"/>
-      <c r="L21" s="53"/>
+      <c r="B21" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="50"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="51"/>
       <c r="M21" s="1"/>
-      <c r="N21" s="51" t="s">
+      <c r="N21" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="52"/>
-      <c r="P21" s="52"/>
-      <c r="Q21" s="52"/>
-      <c r="R21" s="52"/>
-      <c r="S21" s="52"/>
-      <c r="T21" s="52"/>
-      <c r="U21" s="52"/>
-      <c r="V21" s="52"/>
-      <c r="W21" s="52"/>
-      <c r="X21" s="53"/>
+      <c r="O21" s="50"/>
+      <c r="P21" s="50"/>
+      <c r="Q21" s="50"/>
+      <c r="R21" s="50"/>
+      <c r="S21" s="50"/>
+      <c r="T21" s="50"/>
+      <c r="U21" s="50"/>
+      <c r="V21" s="50"/>
+      <c r="W21" s="50"/>
+      <c r="X21" s="51"/>
       <c r="Y21" s="1"/>
-      <c r="Z21" s="51" t="s">
+      <c r="Z21" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="AA21" s="52"/>
-      <c r="AB21" s="52"/>
-      <c r="AC21" s="52"/>
-      <c r="AD21" s="52"/>
-      <c r="AE21" s="52"/>
-      <c r="AF21" s="52"/>
-      <c r="AG21" s="52"/>
-      <c r="AH21" s="52"/>
-      <c r="AI21" s="52"/>
-      <c r="AJ21" s="53"/>
+      <c r="AA21" s="50"/>
+      <c r="AB21" s="50"/>
+      <c r="AC21" s="50"/>
+      <c r="AD21" s="50"/>
+      <c r="AE21" s="50"/>
+      <c r="AF21" s="50"/>
+      <c r="AG21" s="50"/>
+      <c r="AH21" s="50"/>
+      <c r="AI21" s="50"/>
+      <c r="AJ21" s="51"/>
     </row>
     <row r="22" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B22" s="35" t="s">
+      <c r="B22" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="37"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="48"/>
       <c r="M22" s="1"/>
-      <c r="N22" s="35" t="s">
+      <c r="N22" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
-      <c r="S22" s="36"/>
-      <c r="T22" s="36"/>
-      <c r="U22" s="36"/>
-      <c r="V22" s="36"/>
-      <c r="W22" s="36"/>
-      <c r="X22" s="37"/>
+      <c r="O22" s="47"/>
+      <c r="P22" s="47"/>
+      <c r="Q22" s="47"/>
+      <c r="R22" s="47"/>
+      <c r="S22" s="47"/>
+      <c r="T22" s="47"/>
+      <c r="U22" s="47"/>
+      <c r="V22" s="47"/>
+      <c r="W22" s="47"/>
+      <c r="X22" s="48"/>
       <c r="Y22" s="1"/>
-      <c r="Z22" s="35" t="s">
+      <c r="Z22" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AA22" s="36"/>
-      <c r="AB22" s="36"/>
-      <c r="AC22" s="36"/>
-      <c r="AD22" s="36"/>
-      <c r="AE22" s="36"/>
-      <c r="AF22" s="36"/>
-      <c r="AG22" s="36"/>
-      <c r="AH22" s="36"/>
-      <c r="AI22" s="36"/>
-      <c r="AJ22" s="37"/>
+      <c r="AA22" s="47"/>
+      <c r="AB22" s="47"/>
+      <c r="AC22" s="47"/>
+      <c r="AD22" s="47"/>
+      <c r="AE22" s="47"/>
+      <c r="AF22" s="47"/>
+      <c r="AG22" s="47"/>
+      <c r="AH22" s="47"/>
+      <c r="AI22" s="47"/>
+      <c r="AJ22" s="48"/>
     </row>
     <row r="23" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B23" s="31" t="s">
@@ -2592,7 +2580,7 @@
         <f>AVERAGE(I24:J24)</f>
         <v>0.14500000000000002</v>
       </c>
-      <c r="L24" s="38">
+      <c r="L24" s="35">
         <f>AVERAGE(E24,H24,K24)</f>
         <v>0.18166666666666667</v>
       </c>
@@ -2630,7 +2618,7 @@
         <f>AVERAGE(U24:V24)</f>
         <v>0.96</v>
       </c>
-      <c r="X24" s="38">
+      <c r="X24" s="35">
         <f>AVERAGE(Q24,T24,W24)</f>
         <v>0.8666666666666667</v>
       </c>
@@ -2644,7 +2632,7 @@
       <c r="AB24" s="1">
         <v>56.44</v>
       </c>
-      <c r="AC24" s="54">
+      <c r="AC24" s="13">
         <f>AVERAGE(AA24:AB24)</f>
         <v>56.44</v>
       </c>
@@ -2654,7 +2642,7 @@
       <c r="AE24" s="1">
         <v>73.27</v>
       </c>
-      <c r="AF24" s="54">
+      <c r="AF24" s="13">
         <f>AVERAGE(AD24:AE24)</f>
         <v>71.289999999999992</v>
       </c>
@@ -2668,7 +2656,7 @@
         <f>AVERAGE(AG24:AH24)</f>
         <v>66.835000000000008</v>
       </c>
-      <c r="AJ24" s="41">
+      <c r="AJ24" s="29">
         <f>AVERAGE(AC24,AF24,AI24)</f>
         <v>64.855000000000004</v>
       </c>
@@ -2741,7 +2729,7 @@
       <c r="V25" s="1">
         <v>0.97</v>
       </c>
-      <c r="W25" s="56">
+      <c r="W25" s="16">
         <f t="shared" ref="W25:W28" si="24">AVERAGE(U25:V25)</f>
         <v>0.97</v>
       </c>
@@ -2822,7 +2810,7 @@
         <f t="shared" si="20"/>
         <v>0.19500000000000001</v>
       </c>
-      <c r="L26" s="39">
+      <c r="L26" s="36">
         <f t="shared" si="21"/>
         <v>0.20666666666666669</v>
       </c>
@@ -2836,7 +2824,7 @@
       <c r="P26" s="1">
         <v>0.8</v>
       </c>
-      <c r="Q26" s="54">
+      <c r="Q26" s="13">
         <f t="shared" si="22"/>
         <v>0.78500000000000003</v>
       </c>
@@ -2860,7 +2848,7 @@
         <f t="shared" si="24"/>
         <v>0.94499999999999995</v>
       </c>
-      <c r="X26" s="41">
+      <c r="X26" s="29">
         <f t="shared" si="25"/>
         <v>0.84</v>
       </c>
@@ -2898,7 +2886,7 @@
         <f t="shared" si="28"/>
         <v>73.27000000000001</v>
       </c>
-      <c r="AJ26" s="38">
+      <c r="AJ26" s="35">
         <f t="shared" si="29"/>
         <v>65.844999999999999</v>
       </c>
@@ -3052,7 +3040,7 @@
         <f t="shared" si="20"/>
         <v>0.155</v>
       </c>
-      <c r="L28" s="40">
+      <c r="L28" s="37">
         <f t="shared" si="21"/>
         <v>0.18833333333333332</v>
       </c>
@@ -3066,7 +3054,7 @@
       <c r="P28" s="8">
         <v>0.84</v>
       </c>
-      <c r="Q28" s="55">
+      <c r="Q28" s="41">
         <f t="shared" si="22"/>
         <v>0.85499999999999998</v>
       </c>
@@ -3086,11 +3074,11 @@
       <c r="V28" s="8">
         <v>0.97</v>
       </c>
-      <c r="W28" s="57">
+      <c r="W28" s="42">
         <f t="shared" si="24"/>
         <v>0.97499999999999998</v>
       </c>
-      <c r="X28" s="40">
+      <c r="X28" s="37">
         <f t="shared" si="25"/>
         <v>0.87</v>
       </c>
@@ -3104,7 +3092,7 @@
       <c r="AB28" s="8">
         <v>75.25</v>
       </c>
-      <c r="AC28" s="55">
+      <c r="AC28" s="41">
         <f t="shared" si="26"/>
         <v>78.22</v>
       </c>
@@ -3114,7 +3102,7 @@
       <c r="AE28" s="8">
         <v>68.319999999999993</v>
       </c>
-      <c r="AF28" s="55">
+      <c r="AF28" s="41">
         <f t="shared" si="27"/>
         <v>76.239999999999995</v>
       </c>
@@ -3128,38 +3116,38 @@
         <f t="shared" si="28"/>
         <v>68.814999999999998</v>
       </c>
-      <c r="AJ28" s="40">
+      <c r="AJ28" s="37">
         <f t="shared" si="29"/>
         <v>74.424999999999997</v>
       </c>
     </row>
     <row r="31" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="N31" s="48" t="s">
+      <c r="N31" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="O31" s="49"/>
-      <c r="P31" s="49"/>
-      <c r="Q31" s="49"/>
-      <c r="R31" s="49"/>
-      <c r="S31" s="49"/>
-      <c r="T31" s="49"/>
-      <c r="U31" s="49"/>
-      <c r="V31" s="49"/>
-      <c r="W31" s="50"/>
+      <c r="O31" s="44"/>
+      <c r="P31" s="44"/>
+      <c r="Q31" s="44"/>
+      <c r="R31" s="44"/>
+      <c r="S31" s="44"/>
+      <c r="T31" s="44"/>
+      <c r="U31" s="44"/>
+      <c r="V31" s="44"/>
+      <c r="W31" s="45"/>
     </row>
     <row r="32" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="N32" s="35" t="s">
+      <c r="N32" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="O32" s="36"/>
-      <c r="P32" s="36"/>
-      <c r="Q32" s="36"/>
-      <c r="R32" s="36"/>
-      <c r="S32" s="36"/>
-      <c r="T32" s="36"/>
-      <c r="U32" s="36"/>
-      <c r="V32" s="36"/>
-      <c r="W32" s="37"/>
+      <c r="O32" s="47"/>
+      <c r="P32" s="47"/>
+      <c r="Q32" s="47"/>
+      <c r="R32" s="47"/>
+      <c r="S32" s="47"/>
+      <c r="T32" s="47"/>
+      <c r="U32" s="47"/>
+      <c r="V32" s="47"/>
+      <c r="W32" s="48"/>
     </row>
     <row r="33" spans="14:24" x14ac:dyDescent="0.45">
       <c r="N33" s="2" t="s">
@@ -3482,7 +3470,7 @@
         <v>-0.18</v>
       </c>
       <c r="W42" s="21"/>
-      <c r="X42" s="38">
+      <c r="X42" s="35">
         <f t="shared" si="35"/>
         <v>0.47000000000000003</v>
       </c>
@@ -3544,18 +3532,13 @@
       <c r="U44" s="22"/>
       <c r="V44" s="22"/>
       <c r="W44" s="23"/>
-      <c r="X44" s="40">
+      <c r="X44" s="37">
         <f t="shared" si="35"/>
         <v>0.50400000000000011</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B12:L12"/>
-    <mergeCell ref="B22:L22"/>
-    <mergeCell ref="B21:L21"/>
     <mergeCell ref="Z21:AJ21"/>
     <mergeCell ref="N32:W32"/>
     <mergeCell ref="N31:W31"/>
@@ -3568,6 +3551,11 @@
     <mergeCell ref="Z2:AJ2"/>
     <mergeCell ref="Z12:AJ12"/>
     <mergeCell ref="Z22:AJ22"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B12:L12"/>
+    <mergeCell ref="B22:L22"/>
+    <mergeCell ref="B21:L21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -519,6 +519,24 @@
     <xf numFmtId="2" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -526,24 +544,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -848,47 +848,47 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="45"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="51"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="49" t="s">
+      <c r="N2" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
-      <c r="V2" s="50"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="51"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="44"/>
+      <c r="V2" s="44"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="45"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" s="49" t="s">
+      <c r="Z2" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="AA2" s="50"/>
-      <c r="AB2" s="50"/>
-      <c r="AC2" s="50"/>
-      <c r="AD2" s="50"/>
-      <c r="AE2" s="50"/>
-      <c r="AF2" s="50"/>
-      <c r="AG2" s="50"/>
-      <c r="AH2" s="50"/>
-      <c r="AI2" s="50"/>
-      <c r="AJ2" s="51"/>
+      <c r="AA2" s="44"/>
+      <c r="AB2" s="44"/>
+      <c r="AC2" s="44"/>
+      <c r="AD2" s="44"/>
+      <c r="AE2" s="44"/>
+      <c r="AF2" s="44"/>
+      <c r="AG2" s="44"/>
+      <c r="AH2" s="44"/>
+      <c r="AI2" s="44"/>
+      <c r="AJ2" s="45"/>
     </row>
     <row r="3" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B3" s="46" t="s">
@@ -1686,47 +1686,47 @@
       <c r="AJ11" s="1"/>
     </row>
     <row r="12" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="45"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="51"/>
       <c r="M12" s="1"/>
-      <c r="N12" s="43" t="s">
+      <c r="N12" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="44"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="44"/>
-      <c r="R12" s="44"/>
-      <c r="S12" s="44"/>
-      <c r="T12" s="44"/>
-      <c r="U12" s="44"/>
-      <c r="V12" s="44"/>
-      <c r="W12" s="44"/>
-      <c r="X12" s="45"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="50"/>
+      <c r="W12" s="50"/>
+      <c r="X12" s="51"/>
       <c r="Y12" s="1"/>
-      <c r="Z12" s="43" t="s">
+      <c r="Z12" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="AA12" s="44"/>
-      <c r="AB12" s="44"/>
-      <c r="AC12" s="44"/>
-      <c r="AD12" s="44"/>
-      <c r="AE12" s="44"/>
-      <c r="AF12" s="44"/>
-      <c r="AG12" s="44"/>
-      <c r="AH12" s="44"/>
-      <c r="AI12" s="44"/>
-      <c r="AJ12" s="45"/>
+      <c r="AA12" s="50"/>
+      <c r="AB12" s="50"/>
+      <c r="AC12" s="50"/>
+      <c r="AD12" s="50"/>
+      <c r="AE12" s="50"/>
+      <c r="AF12" s="50"/>
+      <c r="AG12" s="50"/>
+      <c r="AH12" s="50"/>
+      <c r="AI12" s="50"/>
+      <c r="AJ12" s="51"/>
     </row>
     <row r="13" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -2358,47 +2358,47 @@
       <c r="AJ20" s="1"/>
     </row>
     <row r="21" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B21" s="49" t="s">
+      <c r="B21" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="50"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="50"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="51"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="45"/>
       <c r="M21" s="1"/>
-      <c r="N21" s="49" t="s">
+      <c r="N21" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="50"/>
-      <c r="P21" s="50"/>
-      <c r="Q21" s="50"/>
-      <c r="R21" s="50"/>
-      <c r="S21" s="50"/>
-      <c r="T21" s="50"/>
-      <c r="U21" s="50"/>
-      <c r="V21" s="50"/>
-      <c r="W21" s="50"/>
-      <c r="X21" s="51"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="44"/>
+      <c r="Q21" s="44"/>
+      <c r="R21" s="44"/>
+      <c r="S21" s="44"/>
+      <c r="T21" s="44"/>
+      <c r="U21" s="44"/>
+      <c r="V21" s="44"/>
+      <c r="W21" s="44"/>
+      <c r="X21" s="45"/>
       <c r="Y21" s="1"/>
-      <c r="Z21" s="49" t="s">
+      <c r="Z21" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="AA21" s="50"/>
-      <c r="AB21" s="50"/>
-      <c r="AC21" s="50"/>
-      <c r="AD21" s="50"/>
-      <c r="AE21" s="50"/>
-      <c r="AF21" s="50"/>
-      <c r="AG21" s="50"/>
-      <c r="AH21" s="50"/>
-      <c r="AI21" s="50"/>
-      <c r="AJ21" s="51"/>
+      <c r="AA21" s="44"/>
+      <c r="AB21" s="44"/>
+      <c r="AC21" s="44"/>
+      <c r="AD21" s="44"/>
+      <c r="AE21" s="44"/>
+      <c r="AF21" s="44"/>
+      <c r="AG21" s="44"/>
+      <c r="AH21" s="44"/>
+      <c r="AI21" s="44"/>
+      <c r="AJ21" s="45"/>
     </row>
     <row r="22" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B22" s="46" t="s">
@@ -3122,18 +3122,18 @@
       </c>
     </row>
     <row r="31" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="N31" s="43" t="s">
+      <c r="N31" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="O31" s="44"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="44"/>
-      <c r="R31" s="44"/>
-      <c r="S31" s="44"/>
-      <c r="T31" s="44"/>
-      <c r="U31" s="44"/>
-      <c r="V31" s="44"/>
-      <c r="W31" s="45"/>
+      <c r="O31" s="50"/>
+      <c r="P31" s="50"/>
+      <c r="Q31" s="50"/>
+      <c r="R31" s="50"/>
+      <c r="S31" s="50"/>
+      <c r="T31" s="50"/>
+      <c r="U31" s="50"/>
+      <c r="V31" s="50"/>
+      <c r="W31" s="51"/>
     </row>
     <row r="32" spans="2:36" x14ac:dyDescent="0.45">
       <c r="N32" s="46" t="s">
@@ -3539,6 +3539,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B12:L12"/>
+    <mergeCell ref="B22:L22"/>
+    <mergeCell ref="B21:L21"/>
     <mergeCell ref="Z21:AJ21"/>
     <mergeCell ref="N32:W32"/>
     <mergeCell ref="N31:W31"/>
@@ -3551,11 +3556,6 @@
     <mergeCell ref="Z2:AJ2"/>
     <mergeCell ref="Z12:AJ12"/>
     <mergeCell ref="Z22:AJ22"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B12:L12"/>
-    <mergeCell ref="B22:L22"/>
-    <mergeCell ref="B21:L21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medenaye\Documents\programs\GitHub\Predictive-MSK-Comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07AFFE26-2AE4-4504-8B9B-95385106C5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2FF445-FE6A-4C15-BA07-5321C432B2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="48">
   <si>
     <t>method</t>
   </si>
@@ -171,6 +171,15 @@
   </si>
   <si>
     <t>RMSE (Nm/kg)</t>
+  </si>
+  <si>
+    <t>bicfemR</t>
+  </si>
+  <si>
+    <t>bicfemL</t>
+  </si>
+  <si>
+    <t>bicfem (avg)</t>
   </si>
 </sst>
 </file>
@@ -401,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -463,11 +472,6 @@
     <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -519,6 +523,24 @@
     <xf numFmtId="2" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -528,22 +550,13 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -839,7 +852,7 @@
     <col min="14" max="14" width="12.9296875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9.265625" customWidth="1"/>
     <col min="20" max="20" width="12.265625" customWidth="1"/>
-    <col min="23" max="23" width="10.06640625" customWidth="1"/>
+    <col min="23" max="23" width="11.86328125" customWidth="1"/>
     <col min="24" max="24" width="10.53125" customWidth="1"/>
     <col min="26" max="26" width="12.9296875" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="9.3984375" customWidth="1"/>
@@ -848,191 +861,191 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="51"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="40"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="43" t="s">
+      <c r="N2" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="44"/>
-      <c r="T2" s="44"/>
-      <c r="U2" s="44"/>
-      <c r="V2" s="44"/>
-      <c r="W2" s="44"/>
-      <c r="X2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="46"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" s="43" t="s">
+      <c r="Z2" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="AA2" s="44"/>
-      <c r="AB2" s="44"/>
-      <c r="AC2" s="44"/>
-      <c r="AD2" s="44"/>
-      <c r="AE2" s="44"/>
-      <c r="AF2" s="44"/>
-      <c r="AG2" s="44"/>
-      <c r="AH2" s="44"/>
-      <c r="AI2" s="44"/>
-      <c r="AJ2" s="45"/>
+      <c r="AA2" s="45"/>
+      <c r="AB2" s="45"/>
+      <c r="AC2" s="45"/>
+      <c r="AD2" s="45"/>
+      <c r="AE2" s="45"/>
+      <c r="AF2" s="45"/>
+      <c r="AG2" s="45"/>
+      <c r="AH2" s="45"/>
+      <c r="AI2" s="45"/>
+      <c r="AJ2" s="46"/>
     </row>
     <row r="3" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="48"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="43"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="46" t="s">
+      <c r="N3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="W3" s="47"/>
-      <c r="X3" s="48"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="42"/>
+      <c r="S3" s="42"/>
+      <c r="T3" s="42"/>
+      <c r="U3" s="42"/>
+      <c r="V3" s="42"/>
+      <c r="W3" s="42"/>
+      <c r="X3" s="43"/>
       <c r="Y3" s="1"/>
-      <c r="Z3" s="46" t="s">
+      <c r="Z3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="AA3" s="47"/>
-      <c r="AB3" s="47"/>
-      <c r="AC3" s="47"/>
-      <c r="AD3" s="47"/>
-      <c r="AE3" s="47"/>
-      <c r="AF3" s="47"/>
-      <c r="AG3" s="47"/>
-      <c r="AH3" s="47"/>
-      <c r="AI3" s="47"/>
-      <c r="AJ3" s="48"/>
+      <c r="AA3" s="42"/>
+      <c r="AB3" s="42"/>
+      <c r="AC3" s="42"/>
+      <c r="AD3" s="42"/>
+      <c r="AE3" s="42"/>
+      <c r="AF3" s="42"/>
+      <c r="AG3" s="42"/>
+      <c r="AH3" s="42"/>
+      <c r="AI3" s="42"/>
+      <c r="AJ3" s="43"/>
     </row>
     <row r="4" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="G4" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="H4" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="27" t="s">
+      <c r="I4" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="27" t="s">
+      <c r="J4" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="32" t="s">
+      <c r="K4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="L4" s="28" t="s">
+      <c r="L4" s="23" t="s">
         <v>42</v>
       </c>
       <c r="M4" s="1"/>
-      <c r="N4" s="31" t="s">
+      <c r="N4" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="O4" s="27" t="s">
+      <c r="O4" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="P4" s="27" t="s">
+      <c r="P4" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="Q4" s="26" t="s">
+      <c r="Q4" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="R4" s="27" t="s">
+      <c r="R4" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="S4" s="27" t="s">
+      <c r="S4" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="T4" s="26" t="s">
+      <c r="T4" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="U4" s="27" t="s">
+      <c r="U4" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="V4" s="27" t="s">
+      <c r="V4" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="W4" s="32" t="s">
+      <c r="W4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="X4" s="28" t="s">
+      <c r="X4" s="23" t="s">
         <v>42</v>
       </c>
       <c r="Y4" s="1"/>
-      <c r="Z4" s="31" t="s">
+      <c r="Z4" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="AA4" s="27" t="s">
+      <c r="AA4" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="AB4" s="27" t="s">
+      <c r="AB4" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="AC4" s="26" t="s">
+      <c r="AC4" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="AD4" s="27" t="s">
+      <c r="AD4" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="AE4" s="27" t="s">
+      <c r="AE4" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="AF4" s="26" t="s">
+      <c r="AF4" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="AG4" s="27" t="s">
+      <c r="AG4" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="AH4" s="27" t="s">
+      <c r="AH4" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="AI4" s="32" t="s">
+      <c r="AI4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="AJ4" s="28" t="s">
+      <c r="AJ4" s="23" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1070,7 +1083,7 @@
         <f>AVERAGE(I5:J5)</f>
         <v>3.87</v>
       </c>
-      <c r="L5" s="35">
+      <c r="L5" s="30">
         <f>AVERAGE(E5,H5,K5)</f>
         <v>4.6466666666666674</v>
       </c>
@@ -1108,7 +1121,7 @@
         <f>AVERAGE(U5:V5)</f>
         <v>0.86</v>
       </c>
-      <c r="X5" s="35">
+      <c r="X5" s="30">
         <f>AVERAGE(Q5,T5,W5)</f>
         <v>0.94</v>
       </c>
@@ -1146,7 +1159,7 @@
         <f>AVERAGE(AG5:AH5)</f>
         <v>76.734999999999999</v>
       </c>
-      <c r="AJ5" s="35">
+      <c r="AJ5" s="30">
         <f>AVERAGE(AC5,AF5,AI5)</f>
         <v>83.83</v>
       </c>
@@ -1185,7 +1198,7 @@
         <f t="shared" ref="K6:K9" si="2">AVERAGE(I6:J6)</f>
         <v>3.9449999999999998</v>
       </c>
-      <c r="L6" s="29">
+      <c r="L6" s="24">
         <f t="shared" ref="L6:L9" si="3">AVERAGE(E6,H6,K6)</f>
         <v>7.0466666666666669</v>
       </c>
@@ -1223,7 +1236,7 @@
         <f t="shared" ref="W6:W9" si="6">AVERAGE(U6:V6)</f>
         <v>0.82499999999999996</v>
       </c>
-      <c r="X6" s="35">
+      <c r="X6" s="30">
         <f t="shared" ref="X6:X9" si="7">AVERAGE(Q6,T6,W6)</f>
         <v>0.89499999999999991</v>
       </c>
@@ -1261,7 +1274,7 @@
         <f t="shared" ref="AI6:AI9" si="10">AVERAGE(AG6:AH6)</f>
         <v>79.704999999999998</v>
       </c>
-      <c r="AJ6" s="29">
+      <c r="AJ6" s="24">
         <f t="shared" ref="AJ6:AJ9" si="11">AVERAGE(AC6,AF6,AI6)</f>
         <v>67.825000000000003</v>
       </c>
@@ -1300,7 +1313,7 @@
         <f t="shared" si="2"/>
         <v>8.745000000000001</v>
       </c>
-      <c r="L7" s="35">
+      <c r="L7" s="30">
         <f t="shared" si="3"/>
         <v>6.0433333333333339</v>
       </c>
@@ -1338,7 +1351,7 @@
         <f t="shared" si="6"/>
         <v>0.51500000000000001</v>
       </c>
-      <c r="X7" s="29">
+      <c r="X7" s="24">
         <f t="shared" si="7"/>
         <v>0.82500000000000007</v>
       </c>
@@ -1376,7 +1389,7 @@
         <f t="shared" si="10"/>
         <v>40.094999999999999</v>
       </c>
-      <c r="AJ7" s="35">
+      <c r="AJ7" s="30">
         <f t="shared" si="11"/>
         <v>71.451666666666668</v>
       </c>
@@ -1415,7 +1428,7 @@
         <f t="shared" si="2"/>
         <v>10.684999999999999</v>
       </c>
-      <c r="L8" s="29">
+      <c r="L8" s="24">
         <f t="shared" si="3"/>
         <v>12.863333333333335</v>
       </c>
@@ -1453,7 +1466,7 @@
         <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="X8" s="29">
+      <c r="X8" s="24">
         <f t="shared" si="7"/>
         <v>0.65166666666666673</v>
       </c>
@@ -1491,7 +1504,7 @@
         <f t="shared" si="10"/>
         <v>28.215</v>
       </c>
-      <c r="AJ8" s="29">
+      <c r="AJ8" s="24">
         <f t="shared" si="11"/>
         <v>31.848333333333333</v>
       </c>
@@ -1530,7 +1543,7 @@
         <f t="shared" si="2"/>
         <v>5.9649999999999999</v>
       </c>
-      <c r="L9" s="30">
+      <c r="L9" s="25">
         <f t="shared" si="3"/>
         <v>8.6466666666666665</v>
       </c>
@@ -1568,7 +1581,7 @@
         <f t="shared" si="6"/>
         <v>0.755</v>
       </c>
-      <c r="X9" s="30">
+      <c r="X9" s="25">
         <f t="shared" si="7"/>
         <v>0.83</v>
       </c>
@@ -1606,7 +1619,7 @@
         <f t="shared" si="10"/>
         <v>52.474999999999994</v>
       </c>
-      <c r="AJ9" s="30">
+      <c r="AJ9" s="25">
         <f t="shared" si="11"/>
         <v>67.493333333333325</v>
       </c>
@@ -1686,47 +1699,47 @@
       <c r="AJ11" s="1"/>
     </row>
     <row r="12" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B12" s="49" t="s">
+      <c r="B12" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="51"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="40"/>
       <c r="M12" s="1"/>
-      <c r="N12" s="49" t="s">
+      <c r="N12" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="50"/>
-      <c r="P12" s="50"/>
-      <c r="Q12" s="50"/>
-      <c r="R12" s="50"/>
-      <c r="S12" s="50"/>
-      <c r="T12" s="50"/>
-      <c r="U12" s="50"/>
-      <c r="V12" s="50"/>
-      <c r="W12" s="50"/>
-      <c r="X12" s="51"/>
+      <c r="O12" s="39"/>
+      <c r="P12" s="39"/>
+      <c r="Q12" s="39"/>
+      <c r="R12" s="39"/>
+      <c r="S12" s="39"/>
+      <c r="T12" s="39"/>
+      <c r="U12" s="39"/>
+      <c r="V12" s="39"/>
+      <c r="W12" s="39"/>
+      <c r="X12" s="40"/>
       <c r="Y12" s="1"/>
-      <c r="Z12" s="49" t="s">
+      <c r="Z12" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="AA12" s="50"/>
-      <c r="AB12" s="50"/>
-      <c r="AC12" s="50"/>
-      <c r="AD12" s="50"/>
-      <c r="AE12" s="50"/>
-      <c r="AF12" s="50"/>
-      <c r="AG12" s="50"/>
-      <c r="AH12" s="50"/>
-      <c r="AI12" s="50"/>
-      <c r="AJ12" s="51"/>
+      <c r="AA12" s="39"/>
+      <c r="AB12" s="39"/>
+      <c r="AC12" s="39"/>
+      <c r="AD12" s="39"/>
+      <c r="AE12" s="39"/>
+      <c r="AF12" s="39"/>
+      <c r="AG12" s="39"/>
+      <c r="AH12" s="39"/>
+      <c r="AI12" s="39"/>
+      <c r="AJ12" s="40"/>
     </row>
     <row r="13" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -1840,7 +1853,7 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="6"/>
-      <c r="L14" s="38">
+      <c r="L14" s="33">
         <f>AVERAGE(E14,H14)</f>
         <v>0.51500000000000001</v>
       </c>
@@ -1871,7 +1884,7 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
       <c r="W14" s="6"/>
-      <c r="X14" s="38">
+      <c r="X14" s="33">
         <f>AVERAGE(Q14,T14)</f>
         <v>0.96750000000000003</v>
       </c>
@@ -1902,7 +1915,7 @@
       <c r="AG14" s="1"/>
       <c r="AH14" s="1"/>
       <c r="AI14" s="6"/>
-      <c r="AJ14" s="38">
+      <c r="AJ14" s="33">
         <f>AVERAGE(AC14,AF14)</f>
         <v>75.25</v>
       </c>
@@ -1934,7 +1947,7 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="6"/>
-      <c r="L15" s="38">
+      <c r="L15" s="33">
         <f>AVERAGE(E15,H15)</f>
         <v>0.82000000000000006</v>
       </c>
@@ -1965,7 +1978,7 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
       <c r="W15" s="6"/>
-      <c r="X15" s="38">
+      <c r="X15" s="33">
         <f>AVERAGE(Q15,T15)</f>
         <v>0.9425</v>
       </c>
@@ -1996,7 +2009,7 @@
       <c r="AG15" s="1"/>
       <c r="AH15" s="1"/>
       <c r="AI15" s="6"/>
-      <c r="AJ15" s="38">
+      <c r="AJ15" s="33">
         <f>AVERAGE(AC15,AF15)</f>
         <v>69.557500000000005</v>
       </c>
@@ -2028,7 +2041,7 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="6"/>
-      <c r="L16" s="39">
+      <c r="L16" s="34">
         <f>AVERAGE(E16,H16)</f>
         <v>1.105</v>
       </c>
@@ -2059,7 +2072,7 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="6"/>
-      <c r="X16" s="39">
+      <c r="X16" s="34">
         <f>AVERAGE(Q16,T16)</f>
         <v>0.89250000000000007</v>
       </c>
@@ -2090,7 +2103,7 @@
       <c r="AG16" s="1"/>
       <c r="AH16" s="1"/>
       <c r="AI16" s="6"/>
-      <c r="AJ16" s="39">
+      <c r="AJ16" s="34">
         <f>AVERAGE(AC16,AF16)</f>
         <v>59.160000000000004</v>
       </c>
@@ -2122,7 +2135,7 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="6"/>
-      <c r="L17" s="39">
+      <c r="L17" s="34">
         <f>AVERAGE(E17,H17)</f>
         <v>0.92500000000000004</v>
       </c>
@@ -2153,7 +2166,7 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="6"/>
-      <c r="X17" s="39">
+      <c r="X17" s="34">
         <f>AVERAGE(Q17,T17)</f>
         <v>0.91250000000000009</v>
       </c>
@@ -2184,7 +2197,7 @@
       <c r="AG17" s="1"/>
       <c r="AH17" s="1"/>
       <c r="AI17" s="6"/>
-      <c r="AJ17" s="39">
+      <c r="AJ17" s="34">
         <f>AVERAGE(AC17,AF17)</f>
         <v>54.952500000000001</v>
       </c>
@@ -2216,7 +2229,7 @@
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
       <c r="K18" s="9"/>
-      <c r="L18" s="40">
+      <c r="L18" s="35">
         <f>AVERAGE(E18,H18)</f>
         <v>1.2374999999999998</v>
       </c>
@@ -2247,7 +2260,7 @@
       <c r="U18" s="8"/>
       <c r="V18" s="8"/>
       <c r="W18" s="9"/>
-      <c r="X18" s="40">
+      <c r="X18" s="35">
         <f>AVERAGE(Q18,T18)</f>
         <v>0.82499999999999996</v>
       </c>
@@ -2278,7 +2291,7 @@
       <c r="AG18" s="8"/>
       <c r="AH18" s="8"/>
       <c r="AI18" s="9"/>
-      <c r="AJ18" s="40">
+      <c r="AJ18" s="35">
         <f>AVERAGE(AC18,AF18)</f>
         <v>54.457499999999996</v>
       </c>
@@ -2358,123 +2371,123 @@
       <c r="AJ20" s="1"/>
     </row>
     <row r="21" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B21" s="43" t="s">
+      <c r="B21" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="46"/>
       <c r="M21" s="1"/>
-      <c r="N21" s="43" t="s">
+      <c r="N21" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="44"/>
-      <c r="P21" s="44"/>
-      <c r="Q21" s="44"/>
-      <c r="R21" s="44"/>
-      <c r="S21" s="44"/>
-      <c r="T21" s="44"/>
-      <c r="U21" s="44"/>
-      <c r="V21" s="44"/>
-      <c r="W21" s="44"/>
-      <c r="X21" s="45"/>
+      <c r="O21" s="45"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="45"/>
+      <c r="R21" s="45"/>
+      <c r="S21" s="45"/>
+      <c r="T21" s="45"/>
+      <c r="U21" s="45"/>
+      <c r="V21" s="45"/>
+      <c r="W21" s="45"/>
+      <c r="X21" s="46"/>
       <c r="Y21" s="1"/>
-      <c r="Z21" s="43" t="s">
+      <c r="Z21" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="AA21" s="44"/>
-      <c r="AB21" s="44"/>
-      <c r="AC21" s="44"/>
-      <c r="AD21" s="44"/>
-      <c r="AE21" s="44"/>
-      <c r="AF21" s="44"/>
-      <c r="AG21" s="44"/>
-      <c r="AH21" s="44"/>
-      <c r="AI21" s="44"/>
-      <c r="AJ21" s="45"/>
+      <c r="AA21" s="45"/>
+      <c r="AB21" s="45"/>
+      <c r="AC21" s="45"/>
+      <c r="AD21" s="45"/>
+      <c r="AE21" s="45"/>
+      <c r="AF21" s="45"/>
+      <c r="AG21" s="45"/>
+      <c r="AH21" s="45"/>
+      <c r="AI21" s="45"/>
+      <c r="AJ21" s="46"/>
     </row>
     <row r="22" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
-      <c r="L22" s="48"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="43"/>
       <c r="M22" s="1"/>
-      <c r="N22" s="46" t="s">
+      <c r="N22" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="O22" s="47"/>
-      <c r="P22" s="47"/>
-      <c r="Q22" s="47"/>
-      <c r="R22" s="47"/>
-      <c r="S22" s="47"/>
-      <c r="T22" s="47"/>
-      <c r="U22" s="47"/>
-      <c r="V22" s="47"/>
-      <c r="W22" s="47"/>
-      <c r="X22" s="48"/>
+      <c r="O22" s="42"/>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="42"/>
+      <c r="R22" s="42"/>
+      <c r="S22" s="42"/>
+      <c r="T22" s="42"/>
+      <c r="U22" s="42"/>
+      <c r="V22" s="42"/>
+      <c r="W22" s="42"/>
+      <c r="X22" s="43"/>
       <c r="Y22" s="1"/>
-      <c r="Z22" s="46" t="s">
+      <c r="Z22" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="AA22" s="47"/>
-      <c r="AB22" s="47"/>
-      <c r="AC22" s="47"/>
-      <c r="AD22" s="47"/>
-      <c r="AE22" s="47"/>
-      <c r="AF22" s="47"/>
-      <c r="AG22" s="47"/>
-      <c r="AH22" s="47"/>
-      <c r="AI22" s="47"/>
-      <c r="AJ22" s="48"/>
+      <c r="AA22" s="42"/>
+      <c r="AB22" s="42"/>
+      <c r="AC22" s="42"/>
+      <c r="AD22" s="42"/>
+      <c r="AE22" s="42"/>
+      <c r="AF22" s="42"/>
+      <c r="AG22" s="42"/>
+      <c r="AH22" s="42"/>
+      <c r="AI22" s="42"/>
+      <c r="AJ22" s="43"/>
     </row>
     <row r="23" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="27" t="s">
+      <c r="D23" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="27" t="s">
+      <c r="F23" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="27" t="s">
+      <c r="G23" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="H23" s="26" t="s">
+      <c r="H23" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="I23" s="27" t="s">
+      <c r="I23" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="J23" s="27" t="s">
+      <c r="J23" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="K23" s="32" t="s">
+      <c r="K23" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="L23" s="33" t="s">
+      <c r="L23" s="28" t="s">
         <v>42</v>
       </c>
       <c r="M23" s="1"/>
@@ -2508,7 +2521,7 @@
       <c r="W23" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="X23" s="33" t="s">
+      <c r="X23" s="28" t="s">
         <v>42</v>
       </c>
       <c r="Y23" s="1"/>
@@ -2542,7 +2555,7 @@
       <c r="AI23" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="AJ23" s="33" t="s">
+      <c r="AJ23" s="28" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2580,7 +2593,7 @@
         <f>AVERAGE(I24:J24)</f>
         <v>0.14500000000000002</v>
       </c>
-      <c r="L24" s="35">
+      <c r="L24" s="30">
         <f>AVERAGE(E24,H24,K24)</f>
         <v>0.18166666666666667</v>
       </c>
@@ -2618,7 +2631,7 @@
         <f>AVERAGE(U24:V24)</f>
         <v>0.96</v>
       </c>
-      <c r="X24" s="35">
+      <c r="X24" s="30">
         <f>AVERAGE(Q24,T24,W24)</f>
         <v>0.8666666666666667</v>
       </c>
@@ -2656,7 +2669,7 @@
         <f>AVERAGE(AG24:AH24)</f>
         <v>66.835000000000008</v>
       </c>
-      <c r="AJ24" s="29">
+      <c r="AJ24" s="24">
         <f>AVERAGE(AC24,AF24,AI24)</f>
         <v>64.855000000000004</v>
       </c>
@@ -2695,7 +2708,7 @@
         <f t="shared" ref="K25:K28" si="20">AVERAGE(I25:J25)</f>
         <v>0.13</v>
       </c>
-      <c r="L25" s="29">
+      <c r="L25" s="24">
         <f t="shared" ref="L25:L28" si="21">AVERAGE(E25,H25,K25)</f>
         <v>0.25666666666666665</v>
       </c>
@@ -2733,7 +2746,7 @@
         <f t="shared" ref="W25:W28" si="24">AVERAGE(U25:V25)</f>
         <v>0.97</v>
       </c>
-      <c r="X25" s="29">
+      <c r="X25" s="24">
         <f t="shared" ref="X25:X28" si="25">AVERAGE(Q25,T25,W25)</f>
         <v>0.64166666666666661</v>
       </c>
@@ -2771,7 +2784,7 @@
         <f t="shared" ref="AI25:AI28" si="28">AVERAGE(AG25:AH25)</f>
         <v>84.655000000000001</v>
       </c>
-      <c r="AJ25" s="29">
+      <c r="AJ25" s="24">
         <f t="shared" ref="AJ25:AJ28" si="29">AVERAGE(AC25,AF25,AI25)</f>
         <v>50.973333333333336</v>
       </c>
@@ -2810,7 +2823,7 @@
         <f t="shared" si="20"/>
         <v>0.19500000000000001</v>
       </c>
-      <c r="L26" s="36">
+      <c r="L26" s="31">
         <f t="shared" si="21"/>
         <v>0.20666666666666669</v>
       </c>
@@ -2848,7 +2861,7 @@
         <f t="shared" si="24"/>
         <v>0.94499999999999995</v>
       </c>
-      <c r="X26" s="29">
+      <c r="X26" s="24">
         <f t="shared" si="25"/>
         <v>0.84</v>
       </c>
@@ -2886,7 +2899,7 @@
         <f t="shared" si="28"/>
         <v>73.27000000000001</v>
       </c>
-      <c r="AJ26" s="35">
+      <c r="AJ26" s="30">
         <f t="shared" si="29"/>
         <v>65.844999999999999</v>
       </c>
@@ -2925,7 +2938,7 @@
         <f t="shared" si="20"/>
         <v>0.2</v>
       </c>
-      <c r="L27" s="29">
+      <c r="L27" s="24">
         <f t="shared" si="21"/>
         <v>0.28000000000000003</v>
       </c>
@@ -2963,7 +2976,7 @@
         <f t="shared" si="24"/>
         <v>0.92500000000000004</v>
       </c>
-      <c r="X27" s="29">
+      <c r="X27" s="24">
         <f t="shared" si="25"/>
         <v>0.66833333333333333</v>
       </c>
@@ -3001,7 +3014,7 @@
         <f t="shared" si="28"/>
         <v>71.784999999999997</v>
       </c>
-      <c r="AJ27" s="29">
+      <c r="AJ27" s="24">
         <f t="shared" si="29"/>
         <v>51.813333333333333</v>
       </c>
@@ -3040,7 +3053,7 @@
         <f t="shared" si="20"/>
         <v>0.155</v>
       </c>
-      <c r="L28" s="37">
+      <c r="L28" s="32">
         <f t="shared" si="21"/>
         <v>0.18833333333333332</v>
       </c>
@@ -3054,7 +3067,7 @@
       <c r="P28" s="8">
         <v>0.84</v>
       </c>
-      <c r="Q28" s="41">
+      <c r="Q28" s="36">
         <f t="shared" si="22"/>
         <v>0.85499999999999998</v>
       </c>
@@ -3074,11 +3087,11 @@
       <c r="V28" s="8">
         <v>0.97</v>
       </c>
-      <c r="W28" s="42">
+      <c r="W28" s="37">
         <f t="shared" si="24"/>
         <v>0.97499999999999998</v>
       </c>
-      <c r="X28" s="37">
+      <c r="X28" s="32">
         <f t="shared" si="25"/>
         <v>0.87</v>
       </c>
@@ -3092,7 +3105,7 @@
       <c r="AB28" s="8">
         <v>75.25</v>
       </c>
-      <c r="AC28" s="41">
+      <c r="AC28" s="36">
         <f t="shared" si="26"/>
         <v>78.22</v>
       </c>
@@ -3102,7 +3115,7 @@
       <c r="AE28" s="8">
         <v>68.319999999999993</v>
       </c>
-      <c r="AF28" s="41">
+      <c r="AF28" s="36">
         <f t="shared" si="27"/>
         <v>76.239999999999995</v>
       </c>
@@ -3116,38 +3129,38 @@
         <f t="shared" si="28"/>
         <v>68.814999999999998</v>
       </c>
-      <c r="AJ28" s="37">
+      <c r="AJ28" s="32">
         <f t="shared" si="29"/>
         <v>74.424999999999997</v>
       </c>
     </row>
     <row r="31" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="N31" s="49" t="s">
+      <c r="N31" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="O31" s="50"/>
-      <c r="P31" s="50"/>
-      <c r="Q31" s="50"/>
-      <c r="R31" s="50"/>
-      <c r="S31" s="50"/>
-      <c r="T31" s="50"/>
-      <c r="U31" s="50"/>
-      <c r="V31" s="50"/>
-      <c r="W31" s="51"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="39"/>
+      <c r="Q31" s="39"/>
+      <c r="R31" s="39"/>
+      <c r="S31" s="39"/>
+      <c r="T31" s="39"/>
+      <c r="U31" s="39"/>
+      <c r="V31" s="39"/>
+      <c r="W31" s="40"/>
     </row>
     <row r="32" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="N32" s="46" t="s">
+      <c r="N32" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="O32" s="47"/>
-      <c r="P32" s="47"/>
-      <c r="Q32" s="47"/>
-      <c r="R32" s="47"/>
-      <c r="S32" s="47"/>
-      <c r="T32" s="47"/>
-      <c r="U32" s="47"/>
-      <c r="V32" s="47"/>
-      <c r="W32" s="48"/>
+      <c r="O32" s="42"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="42"/>
+      <c r="R32" s="42"/>
+      <c r="S32" s="42"/>
+      <c r="T32" s="42"/>
+      <c r="U32" s="42"/>
+      <c r="V32" s="42"/>
+      <c r="W32" s="43"/>
     </row>
     <row r="33" spans="14:24" x14ac:dyDescent="0.45">
       <c r="N33" s="2" t="s">
@@ -3378,10 +3391,16 @@
       <c r="T39" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="U39" s="24"/>
-      <c r="V39" s="24"/>
-      <c r="W39" s="25"/>
-      <c r="X39" s="33" t="s">
+      <c r="U39" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="V39" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="W39" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="X39" s="28" t="s">
         <v>42</v>
       </c>
     </row>
@@ -3409,10 +3428,19 @@
         <f>AVERAGE(R40:S40)</f>
         <v>-0.315</v>
       </c>
-      <c r="W40" s="21"/>
-      <c r="X40" s="34">
-        <f>AVERAGE(Q40,T40,Q34,T34,W34)</f>
-        <v>0.28399999999999997</v>
+      <c r="U40" s="47">
+        <v>0</v>
+      </c>
+      <c r="V40" s="47">
+        <v>0</v>
+      </c>
+      <c r="W40" s="49">
+        <f>AVERAGE(U40:V40)</f>
+        <v>0</v>
+      </c>
+      <c r="X40" s="29">
+        <f>AVERAGE(Q40,T40,Q34,T34,W34,W40)</f>
+        <v>0.23666666666666666</v>
       </c>
     </row>
     <row r="41" spans="14:24" x14ac:dyDescent="0.45">
@@ -3439,10 +3467,19 @@
         <f t="shared" ref="T41:T44" si="34">AVERAGE(R41:S41)</f>
         <v>-0.215</v>
       </c>
-      <c r="W41" s="21"/>
-      <c r="X41" s="29">
-        <f t="shared" ref="X41:X44" si="35">AVERAGE(Q41,T41,Q35,T35,W35)</f>
-        <v>0.23100000000000001</v>
+      <c r="U41" s="47">
+        <v>-0.59</v>
+      </c>
+      <c r="V41" s="47">
+        <v>-0.57999999999999996</v>
+      </c>
+      <c r="W41" s="49">
+        <f t="shared" ref="W41:W44" si="35">AVERAGE(U41:V41)</f>
+        <v>-0.58499999999999996</v>
+      </c>
+      <c r="X41" s="24">
+        <f t="shared" ref="X41:X44" si="36">AVERAGE(Q41,T41,Q35,T35,W35,W41)</f>
+        <v>9.5000000000000015E-2</v>
       </c>
     </row>
     <row r="42" spans="14:24" x14ac:dyDescent="0.45">
@@ -3469,10 +3506,19 @@
         <f t="shared" si="34"/>
         <v>-0.18</v>
       </c>
-      <c r="W42" s="21"/>
-      <c r="X42" s="35">
+      <c r="U42" s="1">
+        <v>-0.41</v>
+      </c>
+      <c r="V42" s="1">
+        <v>-0.41</v>
+      </c>
+      <c r="W42" s="49">
         <f t="shared" si="35"/>
-        <v>0.47000000000000003</v>
+        <v>-0.41</v>
+      </c>
+      <c r="X42" s="30">
+        <f t="shared" si="36"/>
+        <v>0.32333333333333336</v>
       </c>
     </row>
     <row r="43" spans="14:24" x14ac:dyDescent="0.45">
@@ -3499,10 +3545,19 @@
         <f t="shared" si="34"/>
         <v>-3.5000000000000003E-2</v>
       </c>
-      <c r="W43" s="21"/>
-      <c r="X43" s="29">
+      <c r="U43" s="1">
+        <v>-0.56999999999999995</v>
+      </c>
+      <c r="V43" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="W43" s="49">
         <f t="shared" si="35"/>
-        <v>0.30500000000000005</v>
+        <v>-0.22499999999999998</v>
+      </c>
+      <c r="X43" s="24">
+        <f t="shared" si="36"/>
+        <v>0.2166666666666667</v>
       </c>
     </row>
     <row r="44" spans="14:24" x14ac:dyDescent="0.45">
@@ -3529,21 +3584,23 @@
         <f t="shared" si="34"/>
         <v>0.13500000000000001</v>
       </c>
-      <c r="U44" s="22"/>
-      <c r="V44" s="22"/>
-      <c r="W44" s="23"/>
-      <c r="X44" s="37">
+      <c r="U44" s="8">
+        <v>-0.38</v>
+      </c>
+      <c r="V44" s="8">
+        <v>0.82</v>
+      </c>
+      <c r="W44" s="36">
         <f t="shared" si="35"/>
-        <v>0.50400000000000011</v>
+        <v>0.21999999999999997</v>
+      </c>
+      <c r="X44" s="32">
+        <f t="shared" si="36"/>
+        <v>0.45666666666666672</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B12:L12"/>
-    <mergeCell ref="B22:L22"/>
-    <mergeCell ref="B21:L21"/>
     <mergeCell ref="Z21:AJ21"/>
     <mergeCell ref="N32:W32"/>
     <mergeCell ref="N31:W31"/>
@@ -3556,6 +3613,11 @@
     <mergeCell ref="Z2:AJ2"/>
     <mergeCell ref="Z12:AJ12"/>
     <mergeCell ref="Z22:AJ22"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B12:L12"/>
+    <mergeCell ref="B22:L22"/>
+    <mergeCell ref="B21:L21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medenaye\Documents\programs\GitHub\Predictive-MSK-Comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2FF445-FE6A-4C15-BA07-5321C432B2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5C2DB1-B888-4C14-A1F5-62911BEC69E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -410,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -523,6 +523,9 @@
     <xf numFmtId="2" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -548,15 +551,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -861,90 +855,90 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="41"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
-      <c r="V2" s="45"/>
-      <c r="W2" s="45"/>
-      <c r="X2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="46"/>
+      <c r="V2" s="46"/>
+      <c r="W2" s="46"/>
+      <c r="X2" s="47"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" s="44" t="s">
+      <c r="Z2" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="AA2" s="45"/>
-      <c r="AB2" s="45"/>
-      <c r="AC2" s="45"/>
-      <c r="AD2" s="45"/>
-      <c r="AE2" s="45"/>
-      <c r="AF2" s="45"/>
-      <c r="AG2" s="45"/>
-      <c r="AH2" s="45"/>
-      <c r="AI2" s="45"/>
-      <c r="AJ2" s="46"/>
+      <c r="AA2" s="46"/>
+      <c r="AB2" s="46"/>
+      <c r="AC2" s="46"/>
+      <c r="AD2" s="46"/>
+      <c r="AE2" s="46"/>
+      <c r="AF2" s="46"/>
+      <c r="AG2" s="46"/>
+      <c r="AH2" s="46"/>
+      <c r="AI2" s="46"/>
+      <c r="AJ2" s="47"/>
     </row>
     <row r="3" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="44"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="41" t="s">
+      <c r="N3" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="42"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="42"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="42"/>
-      <c r="U3" s="42"/>
-      <c r="V3" s="42"/>
-      <c r="W3" s="42"/>
-      <c r="X3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="44"/>
       <c r="Y3" s="1"/>
-      <c r="Z3" s="41" t="s">
+      <c r="Z3" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="AA3" s="42"/>
-      <c r="AB3" s="42"/>
-      <c r="AC3" s="42"/>
-      <c r="AD3" s="42"/>
-      <c r="AE3" s="42"/>
-      <c r="AF3" s="42"/>
-      <c r="AG3" s="42"/>
-      <c r="AH3" s="42"/>
-      <c r="AI3" s="42"/>
-      <c r="AJ3" s="43"/>
+      <c r="AA3" s="43"/>
+      <c r="AB3" s="43"/>
+      <c r="AC3" s="43"/>
+      <c r="AD3" s="43"/>
+      <c r="AE3" s="43"/>
+      <c r="AF3" s="43"/>
+      <c r="AG3" s="43"/>
+      <c r="AH3" s="43"/>
+      <c r="AI3" s="43"/>
+      <c r="AJ3" s="44"/>
     </row>
     <row r="4" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B4" s="26" t="s">
@@ -1699,47 +1693,47 @@
       <c r="AJ11" s="1"/>
     </row>
     <row r="12" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="41"/>
       <c r="M12" s="1"/>
-      <c r="N12" s="38" t="s">
+      <c r="N12" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="39"/>
-      <c r="S12" s="39"/>
-      <c r="T12" s="39"/>
-      <c r="U12" s="39"/>
-      <c r="V12" s="39"/>
-      <c r="W12" s="39"/>
-      <c r="X12" s="40"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="40"/>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="40"/>
+      <c r="S12" s="40"/>
+      <c r="T12" s="40"/>
+      <c r="U12" s="40"/>
+      <c r="V12" s="40"/>
+      <c r="W12" s="40"/>
+      <c r="X12" s="41"/>
       <c r="Y12" s="1"/>
-      <c r="Z12" s="38" t="s">
+      <c r="Z12" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AA12" s="39"/>
-      <c r="AB12" s="39"/>
-      <c r="AC12" s="39"/>
-      <c r="AD12" s="39"/>
-      <c r="AE12" s="39"/>
-      <c r="AF12" s="39"/>
-      <c r="AG12" s="39"/>
-      <c r="AH12" s="39"/>
-      <c r="AI12" s="39"/>
-      <c r="AJ12" s="40"/>
+      <c r="AA12" s="40"/>
+      <c r="AB12" s="40"/>
+      <c r="AC12" s="40"/>
+      <c r="AD12" s="40"/>
+      <c r="AE12" s="40"/>
+      <c r="AF12" s="40"/>
+      <c r="AG12" s="40"/>
+      <c r="AH12" s="40"/>
+      <c r="AI12" s="40"/>
+      <c r="AJ12" s="41"/>
     </row>
     <row r="13" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -2371,90 +2365,90 @@
       <c r="AJ20" s="1"/>
     </row>
     <row r="21" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B21" s="44" t="s">
+      <c r="B21" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="46"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="46"/>
+      <c r="L21" s="47"/>
       <c r="M21" s="1"/>
-      <c r="N21" s="44" t="s">
+      <c r="N21" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="45"/>
-      <c r="P21" s="45"/>
-      <c r="Q21" s="45"/>
-      <c r="R21" s="45"/>
-      <c r="S21" s="45"/>
-      <c r="T21" s="45"/>
-      <c r="U21" s="45"/>
-      <c r="V21" s="45"/>
-      <c r="W21" s="45"/>
-      <c r="X21" s="46"/>
+      <c r="O21" s="46"/>
+      <c r="P21" s="46"/>
+      <c r="Q21" s="46"/>
+      <c r="R21" s="46"/>
+      <c r="S21" s="46"/>
+      <c r="T21" s="46"/>
+      <c r="U21" s="46"/>
+      <c r="V21" s="46"/>
+      <c r="W21" s="46"/>
+      <c r="X21" s="47"/>
       <c r="Y21" s="1"/>
-      <c r="Z21" s="44" t="s">
+      <c r="Z21" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="AA21" s="45"/>
-      <c r="AB21" s="45"/>
-      <c r="AC21" s="45"/>
-      <c r="AD21" s="45"/>
-      <c r="AE21" s="45"/>
-      <c r="AF21" s="45"/>
-      <c r="AG21" s="45"/>
-      <c r="AH21" s="45"/>
-      <c r="AI21" s="45"/>
-      <c r="AJ21" s="46"/>
+      <c r="AA21" s="46"/>
+      <c r="AB21" s="46"/>
+      <c r="AC21" s="46"/>
+      <c r="AD21" s="46"/>
+      <c r="AE21" s="46"/>
+      <c r="AF21" s="46"/>
+      <c r="AG21" s="46"/>
+      <c r="AH21" s="46"/>
+      <c r="AI21" s="46"/>
+      <c r="AJ21" s="47"/>
     </row>
     <row r="22" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="42"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="44"/>
       <c r="M22" s="1"/>
-      <c r="N22" s="41" t="s">
+      <c r="N22" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="O22" s="42"/>
-      <c r="P22" s="42"/>
-      <c r="Q22" s="42"/>
-      <c r="R22" s="42"/>
-      <c r="S22" s="42"/>
-      <c r="T22" s="42"/>
-      <c r="U22" s="42"/>
-      <c r="V22" s="42"/>
-      <c r="W22" s="42"/>
-      <c r="X22" s="43"/>
+      <c r="O22" s="43"/>
+      <c r="P22" s="43"/>
+      <c r="Q22" s="43"/>
+      <c r="R22" s="43"/>
+      <c r="S22" s="43"/>
+      <c r="T22" s="43"/>
+      <c r="U22" s="43"/>
+      <c r="V22" s="43"/>
+      <c r="W22" s="43"/>
+      <c r="X22" s="44"/>
       <c r="Y22" s="1"/>
-      <c r="Z22" s="41" t="s">
+      <c r="Z22" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="AA22" s="42"/>
-      <c r="AB22" s="42"/>
-      <c r="AC22" s="42"/>
-      <c r="AD22" s="42"/>
-      <c r="AE22" s="42"/>
-      <c r="AF22" s="42"/>
-      <c r="AG22" s="42"/>
-      <c r="AH22" s="42"/>
-      <c r="AI22" s="42"/>
-      <c r="AJ22" s="43"/>
+      <c r="AA22" s="43"/>
+      <c r="AB22" s="43"/>
+      <c r="AC22" s="43"/>
+      <c r="AD22" s="43"/>
+      <c r="AE22" s="43"/>
+      <c r="AF22" s="43"/>
+      <c r="AG22" s="43"/>
+      <c r="AH22" s="43"/>
+      <c r="AI22" s="43"/>
+      <c r="AJ22" s="44"/>
     </row>
     <row r="23" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B23" s="26" t="s">
@@ -3135,32 +3129,32 @@
       </c>
     </row>
     <row r="31" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="N31" s="38" t="s">
+      <c r="N31" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="O31" s="39"/>
-      <c r="P31" s="39"/>
-      <c r="Q31" s="39"/>
-      <c r="R31" s="39"/>
-      <c r="S31" s="39"/>
-      <c r="T31" s="39"/>
-      <c r="U31" s="39"/>
-      <c r="V31" s="39"/>
-      <c r="W31" s="40"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="40"/>
+      <c r="S31" s="40"/>
+      <c r="T31" s="40"/>
+      <c r="U31" s="40"/>
+      <c r="V31" s="40"/>
+      <c r="W31" s="41"/>
     </row>
     <row r="32" spans="2:36" x14ac:dyDescent="0.45">
-      <c r="N32" s="41" t="s">
+      <c r="N32" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="O32" s="42"/>
-      <c r="P32" s="42"/>
-      <c r="Q32" s="42"/>
-      <c r="R32" s="42"/>
-      <c r="S32" s="42"/>
-      <c r="T32" s="42"/>
-      <c r="U32" s="42"/>
-      <c r="V32" s="42"/>
-      <c r="W32" s="43"/>
+      <c r="O32" s="43"/>
+      <c r="P32" s="43"/>
+      <c r="Q32" s="43"/>
+      <c r="R32" s="43"/>
+      <c r="S32" s="43"/>
+      <c r="T32" s="43"/>
+      <c r="U32" s="43"/>
+      <c r="V32" s="43"/>
+      <c r="W32" s="44"/>
     </row>
     <row r="33" spans="14:24" x14ac:dyDescent="0.45">
       <c r="N33" s="2" t="s">
@@ -3397,7 +3391,7 @@
       <c r="V39" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="W39" s="48" t="s">
+      <c r="W39" s="38" t="s">
         <v>47</v>
       </c>
       <c r="X39" s="28" t="s">
@@ -3428,13 +3422,13 @@
         <f>AVERAGE(R40:S40)</f>
         <v>-0.315</v>
       </c>
-      <c r="U40" s="47">
+      <c r="U40" s="1">
         <v>0</v>
       </c>
-      <c r="V40" s="47">
+      <c r="V40" s="1">
         <v>0</v>
       </c>
-      <c r="W40" s="49">
+      <c r="W40" s="13">
         <f>AVERAGE(U40:V40)</f>
         <v>0</v>
       </c>
@@ -3467,13 +3461,13 @@
         <f t="shared" ref="T41:T44" si="34">AVERAGE(R41:S41)</f>
         <v>-0.215</v>
       </c>
-      <c r="U41" s="47">
+      <c r="U41" s="1">
         <v>-0.59</v>
       </c>
-      <c r="V41" s="47">
+      <c r="V41" s="1">
         <v>-0.57999999999999996</v>
       </c>
-      <c r="W41" s="49">
+      <c r="W41" s="13">
         <f t="shared" ref="W41:W44" si="35">AVERAGE(U41:V41)</f>
         <v>-0.58499999999999996</v>
       </c>
@@ -3512,7 +3506,7 @@
       <c r="V42" s="1">
         <v>-0.41</v>
       </c>
-      <c r="W42" s="49">
+      <c r="W42" s="13">
         <f t="shared" si="35"/>
         <v>-0.41</v>
       </c>
@@ -3551,7 +3545,7 @@
       <c r="V43" s="1">
         <v>0.12</v>
       </c>
-      <c r="W43" s="49">
+      <c r="W43" s="13">
         <f t="shared" si="35"/>
         <v>-0.22499999999999998</v>
       </c>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medenaye\Documents\programs\GitHub\Predictive-MSK-Comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5C2DB1-B888-4C14-A1F5-62911BEC69E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7665495D-BA67-4A33-AA7D-C083A4224C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -526,6 +526,24 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -533,24 +551,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -855,47 +855,47 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="41"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="47"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="45" t="s">
+      <c r="N2" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
-      <c r="W2" s="46"/>
-      <c r="X2" s="47"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="40"/>
+      <c r="U2" s="40"/>
+      <c r="V2" s="40"/>
+      <c r="W2" s="40"/>
+      <c r="X2" s="41"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AA2" s="46"/>
-      <c r="AB2" s="46"/>
-      <c r="AC2" s="46"/>
-      <c r="AD2" s="46"/>
-      <c r="AE2" s="46"/>
-      <c r="AF2" s="46"/>
-      <c r="AG2" s="46"/>
-      <c r="AH2" s="46"/>
-      <c r="AI2" s="46"/>
-      <c r="AJ2" s="47"/>
+      <c r="AA2" s="40"/>
+      <c r="AB2" s="40"/>
+      <c r="AC2" s="40"/>
+      <c r="AD2" s="40"/>
+      <c r="AE2" s="40"/>
+      <c r="AF2" s="40"/>
+      <c r="AG2" s="40"/>
+      <c r="AH2" s="40"/>
+      <c r="AI2" s="40"/>
+      <c r="AJ2" s="41"/>
     </row>
     <row r="3" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B3" s="42" t="s">
@@ -1403,14 +1403,14 @@
         <v>9.6550000000000011</v>
       </c>
       <c r="F8" s="1">
-        <v>17.899999999999999</v>
+        <v>17.95</v>
       </c>
       <c r="G8" s="1">
         <v>18.600000000000001</v>
       </c>
       <c r="H8" s="13">
         <f t="shared" si="1"/>
-        <v>18.25</v>
+        <v>18.274999999999999</v>
       </c>
       <c r="I8" s="1">
         <v>10.6</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="L8" s="24">
         <f t="shared" si="3"/>
-        <v>12.863333333333335</v>
+        <v>12.871666666666664</v>
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="5" t="s">
@@ -1693,47 +1693,47 @@
       <c r="AJ11" s="1"/>
     </row>
     <row r="12" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="41"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="47"/>
       <c r="M12" s="1"/>
-      <c r="N12" s="39" t="s">
+      <c r="N12" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="40"/>
-      <c r="P12" s="40"/>
-      <c r="Q12" s="40"/>
-      <c r="R12" s="40"/>
-      <c r="S12" s="40"/>
-      <c r="T12" s="40"/>
-      <c r="U12" s="40"/>
-      <c r="V12" s="40"/>
-      <c r="W12" s="40"/>
-      <c r="X12" s="41"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
+      <c r="S12" s="46"/>
+      <c r="T12" s="46"/>
+      <c r="U12" s="46"/>
+      <c r="V12" s="46"/>
+      <c r="W12" s="46"/>
+      <c r="X12" s="47"/>
       <c r="Y12" s="1"/>
-      <c r="Z12" s="39" t="s">
+      <c r="Z12" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="AA12" s="40"/>
-      <c r="AB12" s="40"/>
-      <c r="AC12" s="40"/>
-      <c r="AD12" s="40"/>
-      <c r="AE12" s="40"/>
-      <c r="AF12" s="40"/>
-      <c r="AG12" s="40"/>
-      <c r="AH12" s="40"/>
-      <c r="AI12" s="40"/>
-      <c r="AJ12" s="41"/>
+      <c r="AA12" s="46"/>
+      <c r="AB12" s="46"/>
+      <c r="AC12" s="46"/>
+      <c r="AD12" s="46"/>
+      <c r="AE12" s="46"/>
+      <c r="AF12" s="46"/>
+      <c r="AG12" s="46"/>
+      <c r="AH12" s="46"/>
+      <c r="AI12" s="46"/>
+      <c r="AJ12" s="47"/>
     </row>
     <row r="13" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -2365,47 +2365,47 @@
       <c r="AJ20" s="1"/>
     </row>
     <row r="21" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B21" s="45" t="s">
+      <c r="B21" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="47"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="41"/>
       <c r="M21" s="1"/>
-      <c r="N21" s="45" t="s">
+      <c r="N21" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="46"/>
-      <c r="P21" s="46"/>
-      <c r="Q21" s="46"/>
-      <c r="R21" s="46"/>
-      <c r="S21" s="46"/>
-      <c r="T21" s="46"/>
-      <c r="U21" s="46"/>
-      <c r="V21" s="46"/>
-      <c r="W21" s="46"/>
-      <c r="X21" s="47"/>
+      <c r="O21" s="40"/>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="40"/>
+      <c r="R21" s="40"/>
+      <c r="S21" s="40"/>
+      <c r="T21" s="40"/>
+      <c r="U21" s="40"/>
+      <c r="V21" s="40"/>
+      <c r="W21" s="40"/>
+      <c r="X21" s="41"/>
       <c r="Y21" s="1"/>
-      <c r="Z21" s="45" t="s">
+      <c r="Z21" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AA21" s="46"/>
-      <c r="AB21" s="46"/>
-      <c r="AC21" s="46"/>
-      <c r="AD21" s="46"/>
-      <c r="AE21" s="46"/>
-      <c r="AF21" s="46"/>
-      <c r="AG21" s="46"/>
-      <c r="AH21" s="46"/>
-      <c r="AI21" s="46"/>
-      <c r="AJ21" s="47"/>
+      <c r="AA21" s="40"/>
+      <c r="AB21" s="40"/>
+      <c r="AC21" s="40"/>
+      <c r="AD21" s="40"/>
+      <c r="AE21" s="40"/>
+      <c r="AF21" s="40"/>
+      <c r="AG21" s="40"/>
+      <c r="AH21" s="40"/>
+      <c r="AI21" s="40"/>
+      <c r="AJ21" s="41"/>
     </row>
     <row r="22" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B22" s="42" t="s">
@@ -2749,14 +2749,14 @@
         <v>2</v>
       </c>
       <c r="AA25" s="1">
-        <v>34.56</v>
+        <v>43.56</v>
       </c>
       <c r="AB25" s="1">
         <v>41.58</v>
       </c>
       <c r="AC25" s="13">
         <f t="shared" ref="AC25:AC28" si="26">AVERAGE(AA25:AB25)</f>
-        <v>38.07</v>
+        <v>42.57</v>
       </c>
       <c r="AD25" s="1">
         <v>24.75</v>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AJ25" s="24">
         <f t="shared" ref="AJ25:AJ28" si="29">AVERAGE(AC25,AF25,AI25)</f>
-        <v>50.973333333333336</v>
+        <v>52.473333333333336</v>
       </c>
     </row>
     <row r="26" spans="2:36" x14ac:dyDescent="0.45">
@@ -3129,18 +3129,18 @@
       </c>
     </row>
     <row r="31" spans="2:36" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="N31" s="39" t="s">
+      <c r="N31" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="O31" s="40"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="40"/>
-      <c r="S31" s="40"/>
-      <c r="T31" s="40"/>
-      <c r="U31" s="40"/>
-      <c r="V31" s="40"/>
-      <c r="W31" s="41"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="46"/>
+      <c r="Q31" s="46"/>
+      <c r="R31" s="46"/>
+      <c r="S31" s="46"/>
+      <c r="T31" s="46"/>
+      <c r="U31" s="46"/>
+      <c r="V31" s="46"/>
+      <c r="W31" s="47"/>
     </row>
     <row r="32" spans="2:36" x14ac:dyDescent="0.45">
       <c r="N32" s="42" t="s">
@@ -3462,18 +3462,18 @@
         <v>-0.215</v>
       </c>
       <c r="U41" s="1">
-        <v>-0.59</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="V41" s="1">
-        <v>-0.57999999999999996</v>
+        <v>-0.56999999999999995</v>
       </c>
       <c r="W41" s="13">
         <f t="shared" ref="W41:W44" si="35">AVERAGE(U41:V41)</f>
-        <v>-0.58499999999999996</v>
+        <v>-0.57499999999999996</v>
       </c>
       <c r="X41" s="24">
         <f t="shared" ref="X41:X44" si="36">AVERAGE(Q41,T41,Q35,T35,W35,W41)</f>
-        <v>9.5000000000000015E-2</v>
+        <v>9.6666666666666679E-2</v>
       </c>
     </row>
     <row r="42" spans="14:24" x14ac:dyDescent="0.45">
@@ -3595,6 +3595,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B12:L12"/>
+    <mergeCell ref="B22:L22"/>
+    <mergeCell ref="B21:L21"/>
     <mergeCell ref="Z21:AJ21"/>
     <mergeCell ref="N32:W32"/>
     <mergeCell ref="N31:W31"/>
@@ -3607,11 +3612,6 @@
     <mergeCell ref="Z2:AJ2"/>
     <mergeCell ref="Z12:AJ12"/>
     <mergeCell ref="Z22:AJ22"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B12:L12"/>
-    <mergeCell ref="B22:L22"/>
-    <mergeCell ref="B21:L21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
